--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96055793</v>
+        <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>97983</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1033,20 +1033,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>S. om Ekmans mosse (Valbricka), Vstm</t>
+          <t>Karmansbo, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537781</v>
+        <v>537910</v>
       </c>
       <c r="R5" t="n">
-        <v>6614966</v>
+        <v>6614923</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,12 +1074,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,27 +1109,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96055793</t>
+          <t>https://artportalen.se/Sighting/137282821</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137153361</v>
+        <v>96055793</v>
       </c>
       <c r="B6" t="n">
-        <v>98253</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,24 +1154,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karmansbo, Vstm</t>
+          <t>S. om Ekmans mosse (Valbricka), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537942</v>
+        <v>537781</v>
       </c>
       <c r="R6" t="n">
-        <v>6614878</v>
+        <v>6614966</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,27 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,16 +1211,137 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055793</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137153361</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98256</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Karmansbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>537942</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6614878</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västra Skedvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137153361</t>
         </is>
@@ -1233,6 +1354,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 42858-2026 artfynd.xlsx
+++ b/artfynd/A 42858-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137153375</v>
       </c>
       <c r="B4" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>137282821</v>
       </c>
       <c r="B5" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>137153361</v>
       </c>
       <c r="B7" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
